--- a/outputs/Sorghum_(local)_percentile_classification_matrix.xlsx
+++ b/outputs/Sorghum_(local)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="93">
   <si>
     <t>2018 Apr</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Yambio</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Minimal</t>
@@ -895,7 +898,7 @@
         <v>79</v>
       </c>
       <c r="Y2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z2" t="s">
         <v>79</v>
@@ -904,19 +907,19 @@
         <v>79</v>
       </c>
       <c r="AB2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="s">
         <v>79</v>
@@ -931,25 +934,25 @@
         <v>79</v>
       </c>
       <c r="AK2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="s">
         <v>79</v>
       </c>
       <c r="AN2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR2" t="s">
         <v>79</v>
@@ -961,13 +964,13 @@
         <v>79</v>
       </c>
       <c r="AU2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:49">
@@ -978,145 +981,145 @@
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
         <v>79</v>
       </c>
       <c r="M3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s">
         <v>79</v>
       </c>
       <c r="T3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s">
         <v>79</v>
       </c>
       <c r="V3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="s">
         <v>79</v>
       </c>
       <c r="Z3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB3" t="s">
         <v>81</v>
       </c>
-      <c r="AB3" t="s">
-        <v>80</v>
-      </c>
       <c r="AC3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AD3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AE3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AT3" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>80</v>
-      </c>
       <c r="AU3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:49">
@@ -1190,37 +1193,37 @@
         <v>79</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD4" t="s">
         <v>79</v>
       </c>
       <c r="AE4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="s">
         <v>79</v>
       </c>
       <c r="AH4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI4" t="s">
         <v>79</v>
@@ -1229,19 +1232,19 @@
         <v>79</v>
       </c>
       <c r="AK4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="s">
         <v>79</v>
       </c>
       <c r="AO4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP4" t="s">
         <v>79</v>
@@ -1250,7 +1253,7 @@
         <v>79</v>
       </c>
       <c r="AR4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS4" t="s">
         <v>79</v>
@@ -1259,13 +1262,13 @@
         <v>79</v>
       </c>
       <c r="AU4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:49">
@@ -1336,40 +1339,40 @@
         <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD5" t="s">
         <v>79</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="s">
         <v>79</v>
       </c>
       <c r="AG5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="s">
         <v>79</v>
@@ -1408,13 +1411,13 @@
         <v>79</v>
       </c>
       <c r="AU5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:49">
@@ -1545,7 +1548,7 @@
         <v>79</v>
       </c>
       <c r="AQ6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR6" t="s">
         <v>79</v>
@@ -1557,13 +1560,13 @@
         <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:49">
@@ -1637,7 +1640,7 @@
         <v>79</v>
       </c>
       <c r="X7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7" t="s">
         <v>79</v>
@@ -1655,7 +1658,7 @@
         <v>79</v>
       </c>
       <c r="AD7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="s">
         <v>79</v>
@@ -1670,7 +1673,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s">
         <v>79</v>
@@ -1691,7 +1694,7 @@
         <v>79</v>
       </c>
       <c r="AP7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ7" t="s">
         <v>79</v>
@@ -1706,13 +1709,13 @@
         <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:49">
@@ -1723,16 +1726,16 @@
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
         <v>79</v>
@@ -1741,7 +1744,7 @@
         <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
         <v>79</v>
@@ -1756,22 +1759,22 @@
         <v>79</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O8" t="s">
         <v>79</v>
       </c>
       <c r="P8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="s">
         <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T8" t="s">
         <v>79</v>
@@ -1855,13 +1858,13 @@
         <v>79</v>
       </c>
       <c r="AU8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:49">
@@ -1872,10 +1875,10 @@
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>79</v>
@@ -1887,22 +1890,22 @@
         <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K9" t="s">
         <v>79</v>
       </c>
       <c r="L9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
         <v>79</v>
@@ -1911,106 +1914,106 @@
         <v>79</v>
       </c>
       <c r="P9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH9" t="s">
         <v>81</v>
       </c>
-      <c r="AG9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>80</v>
-      </c>
       <c r="AI9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s">
         <v>81</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK9" t="s">
+      <c r="AO9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS9" t="s">
         <v>81</v>
       </c>
-      <c r="AL9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>80</v>
-      </c>
       <c r="AT9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AU9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:49">
@@ -2123,19 +2126,19 @@
         <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP10" t="s">
         <v>79</v>
@@ -2153,13 +2156,13 @@
         <v>79</v>
       </c>
       <c r="AU10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:49">
@@ -2281,13 +2284,13 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="s">
         <v>79</v>
       </c>
       <c r="AP11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ11" t="s">
         <v>79</v>
@@ -2302,13 +2305,13 @@
         <v>79</v>
       </c>
       <c r="AU11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:49">
@@ -2382,10 +2385,10 @@
         <v>79</v>
       </c>
       <c r="X12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z12" t="s">
         <v>79</v>
@@ -2394,7 +2397,7 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s">
         <v>79</v>
@@ -2412,7 +2415,7 @@
         <v>79</v>
       </c>
       <c r="AH12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s">
         <v>79</v>
@@ -2421,10 +2424,10 @@
         <v>79</v>
       </c>
       <c r="AK12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="s">
         <v>79</v>
@@ -2445,19 +2448,19 @@
         <v>79</v>
       </c>
       <c r="AS12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT12" t="s">
         <v>79</v>
       </c>
       <c r="AU12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:49">
@@ -2528,10 +2531,10 @@
         <v>79</v>
       </c>
       <c r="W13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s">
         <v>79</v>
@@ -2540,7 +2543,7 @@
         <v>79</v>
       </c>
       <c r="AA13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="s">
         <v>79</v>
@@ -2564,49 +2567,49 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO13" t="s">
         <v>79</v>
       </c>
       <c r="AP13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT13" t="s">
         <v>79</v>
       </c>
       <c r="AU13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AW13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:49">
@@ -2635,7 +2638,7 @@
         <v>79</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s">
         <v>79</v>
@@ -2650,49 +2653,49 @@
         <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="s">
         <v>79</v>
       </c>
       <c r="R14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S14" t="s">
         <v>79</v>
       </c>
       <c r="T14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
       </c>
       <c r="W14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X14" t="s">
         <v>79</v>
       </c>
       <c r="Y14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC14" t="s">
         <v>79</v>
@@ -2704,43 +2707,43 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH14" t="s">
         <v>81</v>
       </c>
-      <c r="AH14" t="s">
-        <v>80</v>
-      </c>
       <c r="AI14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL14" t="s">
         <v>81</v>
       </c>
-      <c r="AJ14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>80</v>
-      </c>
       <c r="AM14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s">
         <v>81</v>
       </c>
-      <c r="AN14" t="s">
-        <v>80</v>
-      </c>
       <c r="AO14" t="s">
         <v>79</v>
       </c>
       <c r="AP14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS14" t="s">
         <v>79</v>
@@ -2749,13 +2752,13 @@
         <v>79</v>
       </c>
       <c r="AU14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW14" t="s">
         <v>85</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW14" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:49">
@@ -2766,10 +2769,10 @@
         <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
         <v>79</v>
@@ -2778,133 +2781,133 @@
         <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L15" t="s">
         <v>79</v>
       </c>
       <c r="M15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O15" t="s">
         <v>79</v>
       </c>
       <c r="P15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R15" t="s">
         <v>79</v>
       </c>
       <c r="S15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s">
         <v>79</v>
       </c>
       <c r="U15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W15" t="s">
         <v>79</v>
       </c>
       <c r="X15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF15" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG15" t="s">
         <v>81</v>
       </c>
-      <c r="AG15" t="s">
-        <v>80</v>
-      </c>
       <c r="AH15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s">
         <v>81</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>80</v>
-      </c>
       <c r="AK15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR15" t="s">
         <v>79</v>
       </c>
       <c r="AS15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AT15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AV15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -2972,19 +2975,19 @@
         <v>79</v>
       </c>
       <c r="V16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="s">
         <v>79</v>
       </c>
       <c r="Z16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s">
         <v>79</v>
@@ -2999,40 +3002,40 @@
         <v>79</v>
       </c>
       <c r="AE16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s">
         <v>79</v>
       </c>
       <c r="AJ16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM16" t="s">
         <v>79</v>
       </c>
       <c r="AN16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ16" t="s">
         <v>79</v>
@@ -3047,13 +3050,13 @@
         <v>79</v>
       </c>
       <c r="AU16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AW16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:49">
@@ -3121,19 +3124,19 @@
         <v>79</v>
       </c>
       <c r="V17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W17" t="s">
         <v>79</v>
       </c>
       <c r="X17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA17" t="s">
         <v>79</v>
@@ -3142,19 +3145,19 @@
         <v>79</v>
       </c>
       <c r="AC17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE17" t="s">
         <v>79</v>
       </c>
       <c r="AF17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s">
         <v>79</v>
@@ -3166,28 +3169,28 @@
         <v>79</v>
       </c>
       <c r="AK17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM17" t="s">
         <v>79</v>
       </c>
       <c r="AN17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP17" t="s">
         <v>79</v>
       </c>
       <c r="AQ17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS17" t="s">
         <v>79</v>
@@ -3196,13 +3199,13 @@
         <v>79</v>
       </c>
       <c r="AU17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:49">
@@ -3270,25 +3273,25 @@
         <v>79</v>
       </c>
       <c r="V18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC18" t="s">
         <v>79</v>
@@ -3297,46 +3300,46 @@
         <v>79</v>
       </c>
       <c r="AE18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG18" t="s">
         <v>79</v>
       </c>
       <c r="AH18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ18" t="s">
         <v>79</v>
       </c>
       <c r="AK18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS18" t="s">
         <v>79</v>
@@ -3345,13 +3348,13 @@
         <v>79</v>
       </c>
       <c r="AU18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:49">
@@ -3437,10 +3440,10 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD19" t="s">
         <v>79</v>
@@ -3494,13 +3497,13 @@
         <v>79</v>
       </c>
       <c r="AU19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:49">
@@ -3511,31 +3514,31 @@
         <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s">
         <v>79</v>
       </c>
       <c r="J20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
         <v>79</v>
@@ -3553,88 +3556,88 @@
         <v>79</v>
       </c>
       <c r="Q20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S20" t="s">
         <v>79</v>
       </c>
       <c r="T20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W20" t="s">
         <v>79</v>
       </c>
       <c r="X20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s">
         <v>79</v>
       </c>
       <c r="AK20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS20" t="s">
         <v>79</v>
@@ -3643,13 +3646,13 @@
         <v>79</v>
       </c>
       <c r="AU20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AV20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:49">
@@ -3744,7 +3747,7 @@
         <v>79</v>
       </c>
       <c r="AE21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF21" t="s">
         <v>79</v>
@@ -3792,13 +3795,13 @@
         <v>79</v>
       </c>
       <c r="AU21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:49">
@@ -3869,34 +3872,34 @@
         <v>79</v>
       </c>
       <c r="W22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X22" t="s">
         <v>79</v>
       </c>
       <c r="Y22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG22" t="s">
         <v>79</v>
@@ -3905,31 +3908,31 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s">
         <v>79</v>
       </c>
       <c r="AK22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s">
         <v>79</v>
       </c>
       <c r="AN22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="s">
         <v>79</v>
       </c>
       <c r="AP22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR22" t="s">
         <v>79</v>
@@ -3941,13 +3944,13 @@
         <v>79</v>
       </c>
       <c r="AU22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AW22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:49">
@@ -3985,7 +3988,7 @@
         <v>79</v>
       </c>
       <c r="L23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M23" t="s">
         <v>79</v>
@@ -4018,7 +4021,7 @@
         <v>79</v>
       </c>
       <c r="W23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X23" t="s">
         <v>79</v>
@@ -4045,7 +4048,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG23" t="s">
         <v>79</v>
@@ -4063,7 +4066,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s">
         <v>79</v>
@@ -4081,22 +4084,22 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AS23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AT23" t="s">
         <v>79</v>
       </c>
       <c r="AU23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AW23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:49">
@@ -4113,19 +4116,19 @@
         <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
         <v>79</v>
       </c>
       <c r="I24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J24" t="s">
         <v>79</v>
@@ -4152,10 +4155,10 @@
         <v>79</v>
       </c>
       <c r="R24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T24" t="s">
         <v>79</v>
@@ -4167,22 +4170,22 @@
         <v>79</v>
       </c>
       <c r="W24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="s">
         <v>79</v>
       </c>
       <c r="Z24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s">
         <v>79</v>
@@ -4191,61 +4194,61 @@
         <v>79</v>
       </c>
       <c r="AE24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s">
         <v>79</v>
       </c>
       <c r="AL24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AQ24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AT24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU24" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>90</v>
+      </c>
+      <c r="AW24" t="s">
         <v>86</v>
-      </c>
-      <c r="AV24" t="s">
-        <v>89</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:49">
@@ -4376,7 +4379,7 @@
         <v>79</v>
       </c>
       <c r="AQ25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR25" t="s">
         <v>79</v>
@@ -4388,13 +4391,13 @@
         <v>79</v>
       </c>
       <c r="AU25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:49">
@@ -4468,25 +4471,25 @@
         <v>79</v>
       </c>
       <c r="X26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s">
         <v>79</v>
       </c>
       <c r="Z26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC26" t="s">
         <v>79</v>
       </c>
       <c r="AD26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE26" t="s">
         <v>79</v>
@@ -4495,16 +4498,16 @@
         <v>79</v>
       </c>
       <c r="AG26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="s">
         <v>79</v>
@@ -4513,22 +4516,22 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP26" t="s">
         <v>79</v>
       </c>
       <c r="AQ26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS26" t="s">
         <v>79</v>
@@ -4537,13 +4540,13 @@
         <v>79</v>
       </c>
       <c r="AU26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:49">
@@ -4554,28 +4557,28 @@
         <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s">
         <v>79</v>
@@ -4587,28 +4590,28 @@
         <v>79</v>
       </c>
       <c r="N27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O27" t="s">
         <v>79</v>
       </c>
       <c r="P27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S27" t="s">
         <v>79</v>
       </c>
       <c r="T27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V27" t="s">
         <v>79</v>
@@ -4650,31 +4653,31 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AP27" t="s">
         <v>79</v>
       </c>
       <c r="AQ27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR27" t="s">
         <v>79</v>
@@ -4686,13 +4689,13 @@
         <v>79</v>
       </c>
       <c r="AU27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AV27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:49">
@@ -4766,13 +4769,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA28" t="s">
         <v>79</v>
@@ -4781,52 +4784,52 @@
         <v>79</v>
       </c>
       <c r="AC28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AE28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s">
         <v>79</v>
       </c>
       <c r="AK28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AL28" t="s">
         <v>79</v>
       </c>
       <c r="AM28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AN28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AO28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AQ28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS28" t="s">
         <v>79</v>
@@ -4835,13 +4838,13 @@
         <v>79</v>
       </c>
       <c r="AU28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:49">
@@ -4921,10 +4924,10 @@
         <v>79</v>
       </c>
       <c r="Z29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="s">
         <v>79</v>
@@ -4984,13 +4987,13 @@
         <v>79</v>
       </c>
       <c r="AU29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AV29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AW29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:49">
@@ -5001,67 +5004,67 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
         <v>79</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s">
         <v>79</v>
       </c>
       <c r="K30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N30" t="s">
         <v>79</v>
       </c>
       <c r="O30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P30" t="s">
         <v>79</v>
       </c>
       <c r="Q30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T30" t="s">
         <v>79</v>
       </c>
       <c r="U30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X30" t="s">
         <v>79</v>
@@ -5073,31 +5076,31 @@
         <v>79</v>
       </c>
       <c r="AA30" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB30" t="s">
         <v>81</v>
       </c>
-      <c r="AB30" t="s">
-        <v>80</v>
-      </c>
       <c r="AC30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s">
         <v>79</v>
       </c>
       <c r="AE30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF30" t="s">
         <v>79</v>
       </c>
       <c r="AG30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AJ30" t="s">
         <v>79</v>
@@ -5121,10 +5124,10 @@
         <v>79</v>
       </c>
       <c r="AQ30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AR30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AS30" t="s">
         <v>79</v>
@@ -5133,13 +5136,13 @@
         <v>79</v>
       </c>
       <c r="AU30" t="s">
+        <v>86</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW30" t="s">
         <v>85</v>
-      </c>
-      <c r="AV30" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW30" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:49">
@@ -5147,16 +5150,16 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
         <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
         <v>79</v>
@@ -5171,10 +5174,10 @@
         <v>79</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L31" t="s">
         <v>79</v>
@@ -5189,106 +5192,106 @@
         <v>79</v>
       </c>
       <c r="P31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q31" t="s">
         <v>79</v>
       </c>
       <c r="R31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T31" t="s">
         <v>79</v>
       </c>
       <c r="U31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Z31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AC31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD31" t="s">
         <v>79</v>
       </c>
       <c r="AE31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP31" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS31" t="s">
         <v>81</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP31" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR31" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS31" t="s">
-        <v>80</v>
-      </c>
       <c r="AT31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AU31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AV31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AW31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_(local)_percentile_classification_matrix.xlsx
+++ b/outputs/Sorghum_(local)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="82">
   <si>
     <t>2018 Apr</t>
   </si>
@@ -259,40 +259,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>16%</t>
-  </si>
-  <si>
-    <t>9%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>27%</t>
   </si>
 </sst>
 </file>
@@ -919,7 +886,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG2" t="s">
         <v>79</v>
@@ -937,7 +904,7 @@
         <v>80</v>
       </c>
       <c r="AL2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM2" t="s">
         <v>79</v>
@@ -964,13 +931,13 @@
         <v>79</v>
       </c>
       <c r="AU2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:49">
@@ -1050,55 +1017,55 @@
         <v>79</v>
       </c>
       <c r="Z3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AE3" t="s">
         <v>80</v>
       </c>
       <c r="AF3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AG3" t="s">
         <v>80</v>
       </c>
       <c r="AH3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="s">
         <v>80</v>
       </c>
       <c r="AK3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="s">
         <v>79</v>
       </c>
       <c r="AN3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ3" t="s">
         <v>80</v>
@@ -1110,16 +1077,16 @@
         <v>80</v>
       </c>
       <c r="AT3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AU3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AV3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AW3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:49">
@@ -1193,7 +1160,7 @@
         <v>79</v>
       </c>
       <c r="X4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4" t="s">
         <v>80</v>
@@ -1205,7 +1172,7 @@
         <v>80</v>
       </c>
       <c r="AB4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s">
         <v>80</v>
@@ -1214,7 +1181,7 @@
         <v>79</v>
       </c>
       <c r="AE4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF4" t="s">
         <v>80</v>
@@ -1223,7 +1190,7 @@
         <v>79</v>
       </c>
       <c r="AH4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s">
         <v>79</v>
@@ -1262,13 +1229,13 @@
         <v>79</v>
       </c>
       <c r="AU4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:49">
@@ -1339,40 +1306,40 @@
         <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD5" t="s">
         <v>79</v>
       </c>
       <c r="AE5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="s">
         <v>79</v>
       </c>
       <c r="AG5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s">
         <v>79</v>
@@ -1411,13 +1378,13 @@
         <v>79</v>
       </c>
       <c r="AU5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:49">
@@ -1548,7 +1515,7 @@
         <v>79</v>
       </c>
       <c r="AQ6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR6" t="s">
         <v>79</v>
@@ -1560,13 +1527,13 @@
         <v>79</v>
       </c>
       <c r="AU6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:49">
@@ -1640,7 +1607,7 @@
         <v>79</v>
       </c>
       <c r="X7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y7" t="s">
         <v>79</v>
@@ -1673,7 +1640,7 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s">
         <v>79</v>
@@ -1709,13 +1676,13 @@
         <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:49">
@@ -1729,13 +1696,13 @@
         <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s">
         <v>79</v>
@@ -1771,7 +1738,7 @@
         <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S8" t="s">
         <v>80</v>
@@ -1858,13 +1825,13 @@
         <v>79</v>
       </c>
       <c r="AU8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:49">
@@ -1938,13 +1905,13 @@
         <v>80</v>
       </c>
       <c r="X9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Y9" t="s">
         <v>80</v>
       </c>
       <c r="Z9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="s">
         <v>80</v>
@@ -1962,37 +1929,37 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AG9" t="s">
         <v>80</v>
       </c>
       <c r="AH9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s">
         <v>79</v>
       </c>
       <c r="AK9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="s">
         <v>79</v>
       </c>
       <c r="AM9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AP9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ9" t="s">
         <v>80</v>
@@ -2001,19 +1968,19 @@
         <v>79</v>
       </c>
       <c r="AS9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AT9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AU9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AV9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AW9" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:49">
@@ -2126,19 +2093,19 @@
         <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AN10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP10" t="s">
         <v>79</v>
@@ -2156,13 +2123,13 @@
         <v>79</v>
       </c>
       <c r="AU10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:49">
@@ -2284,13 +2251,13 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO11" t="s">
         <v>79</v>
       </c>
       <c r="AP11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ11" t="s">
         <v>79</v>
@@ -2305,13 +2272,13 @@
         <v>79</v>
       </c>
       <c r="AU11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:49">
@@ -2385,7 +2352,7 @@
         <v>79</v>
       </c>
       <c r="X12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y12" t="s">
         <v>80</v>
@@ -2397,7 +2364,7 @@
         <v>79</v>
       </c>
       <c r="AB12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC12" t="s">
         <v>79</v>
@@ -2415,7 +2382,7 @@
         <v>79</v>
       </c>
       <c r="AH12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s">
         <v>79</v>
@@ -2427,7 +2394,7 @@
         <v>80</v>
       </c>
       <c r="AL12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM12" t="s">
         <v>79</v>
@@ -2448,19 +2415,19 @@
         <v>79</v>
       </c>
       <c r="AS12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AT12" t="s">
         <v>79</v>
       </c>
       <c r="AU12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:49">
@@ -2567,49 +2534,49 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s">
         <v>80</v>
       </c>
       <c r="AN13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s">
         <v>79</v>
       </c>
       <c r="AP13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AT13" t="s">
         <v>79</v>
       </c>
       <c r="AU13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AW13" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:49">
@@ -2710,37 +2677,37 @@
         <v>80</v>
       </c>
       <c r="AG14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s">
         <v>80</v>
       </c>
       <c r="AL14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="s">
         <v>79</v>
       </c>
       <c r="AP14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR14" t="s">
         <v>80</v>
@@ -2752,13 +2719,13 @@
         <v>79</v>
       </c>
       <c r="AU14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AV14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AW14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:49">
@@ -2838,7 +2805,7 @@
         <v>80</v>
       </c>
       <c r="Z15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="s">
         <v>80</v>
@@ -2856,37 +2823,37 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AG15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s">
         <v>80</v>
       </c>
       <c r="AI15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AO15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ15" t="s">
         <v>80</v>
@@ -2895,19 +2862,19 @@
         <v>79</v>
       </c>
       <c r="AS15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AT15" t="s">
         <v>80</v>
       </c>
       <c r="AU15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AV15" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AW15" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -2978,7 +2945,7 @@
         <v>80</v>
       </c>
       <c r="W16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X16" t="s">
         <v>80</v>
@@ -3002,25 +2969,25 @@
         <v>79</v>
       </c>
       <c r="AE16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG16" t="s">
         <v>80</v>
       </c>
       <c r="AH16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s">
         <v>79</v>
       </c>
       <c r="AJ16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s">
         <v>80</v>
@@ -3029,13 +2996,13 @@
         <v>79</v>
       </c>
       <c r="AN16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ16" t="s">
         <v>79</v>
@@ -3050,13 +3017,13 @@
         <v>79</v>
       </c>
       <c r="AU16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV16" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AW16" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:49">
@@ -3130,7 +3097,7 @@
         <v>79</v>
       </c>
       <c r="X17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y17" t="s">
         <v>80</v>
@@ -3148,7 +3115,7 @@
         <v>80</v>
       </c>
       <c r="AD17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE17" t="s">
         <v>79</v>
@@ -3178,7 +3145,7 @@
         <v>79</v>
       </c>
       <c r="AN17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO17" t="s">
         <v>80</v>
@@ -3187,7 +3154,7 @@
         <v>79</v>
       </c>
       <c r="AQ17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR17" t="s">
         <v>80</v>
@@ -3199,13 +3166,13 @@
         <v>79</v>
       </c>
       <c r="AU17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:49">
@@ -3273,13 +3240,13 @@
         <v>79</v>
       </c>
       <c r="V18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W18" t="s">
         <v>80</v>
       </c>
       <c r="X18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y18" t="s">
         <v>80</v>
@@ -3309,19 +3276,19 @@
         <v>79</v>
       </c>
       <c r="AH18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="s">
         <v>79</v>
       </c>
       <c r="AK18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="s">
         <v>80</v>
@@ -3330,10 +3297,10 @@
         <v>80</v>
       </c>
       <c r="AO18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AQ18" t="s">
         <v>80</v>
@@ -3348,13 +3315,13 @@
         <v>79</v>
       </c>
       <c r="AU18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AW18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:49">
@@ -3440,10 +3407,10 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD19" t="s">
         <v>79</v>
@@ -3497,13 +3464,13 @@
         <v>79</v>
       </c>
       <c r="AU19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:49">
@@ -3577,7 +3544,7 @@
         <v>79</v>
       </c>
       <c r="X20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y20" t="s">
         <v>80</v>
@@ -3592,10 +3559,10 @@
         <v>80</v>
       </c>
       <c r="AC20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AD20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AE20" t="s">
         <v>80</v>
@@ -3607,10 +3574,10 @@
         <v>80</v>
       </c>
       <c r="AH20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="s">
         <v>79</v>
@@ -3619,7 +3586,7 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="s">
         <v>80</v>
@@ -3628,10 +3595,10 @@
         <v>80</v>
       </c>
       <c r="AO20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ20" t="s">
         <v>80</v>
@@ -3646,13 +3613,13 @@
         <v>79</v>
       </c>
       <c r="AU20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AV20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:49">
@@ -3747,7 +3714,7 @@
         <v>79</v>
       </c>
       <c r="AE21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s">
         <v>79</v>
@@ -3795,13 +3762,13 @@
         <v>79</v>
       </c>
       <c r="AU21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:49">
@@ -3884,13 +3851,13 @@
         <v>80</v>
       </c>
       <c r="AA22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB22" t="s">
         <v>80</v>
       </c>
       <c r="AC22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD22" t="s">
         <v>80</v>
@@ -3899,7 +3866,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG22" t="s">
         <v>79</v>
@@ -3914,7 +3881,7 @@
         <v>79</v>
       </c>
       <c r="AK22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s">
         <v>80</v>
@@ -3944,13 +3911,13 @@
         <v>79</v>
       </c>
       <c r="AU22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV22" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AW22" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:49">
@@ -3988,7 +3955,7 @@
         <v>79</v>
       </c>
       <c r="L23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M23" t="s">
         <v>79</v>
@@ -4021,7 +3988,7 @@
         <v>79</v>
       </c>
       <c r="W23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X23" t="s">
         <v>79</v>
@@ -4066,7 +4033,7 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s">
         <v>79</v>
@@ -4084,22 +4051,22 @@
         <v>79</v>
       </c>
       <c r="AR23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AS23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AT23" t="s">
         <v>79</v>
       </c>
       <c r="AU23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV23" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AW23" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:49">
@@ -4200,7 +4167,7 @@
         <v>80</v>
       </c>
       <c r="AG24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s">
         <v>80</v>
@@ -4224,10 +4191,10 @@
         <v>80</v>
       </c>
       <c r="AO24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ24" t="s">
         <v>80</v>
@@ -4236,19 +4203,19 @@
         <v>80</v>
       </c>
       <c r="AS24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AT24" t="s">
         <v>80</v>
       </c>
       <c r="AU24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AV24" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AW24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:49">
@@ -4379,7 +4346,7 @@
         <v>79</v>
       </c>
       <c r="AQ25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR25" t="s">
         <v>79</v>
@@ -4391,13 +4358,13 @@
         <v>79</v>
       </c>
       <c r="AU25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:49">
@@ -4477,7 +4444,7 @@
         <v>79</v>
       </c>
       <c r="Z26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA26" t="s">
         <v>80</v>
@@ -4489,7 +4456,7 @@
         <v>79</v>
       </c>
       <c r="AD26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE26" t="s">
         <v>79</v>
@@ -4498,13 +4465,13 @@
         <v>79</v>
       </c>
       <c r="AG26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s">
         <v>80</v>
@@ -4522,16 +4489,16 @@
         <v>80</v>
       </c>
       <c r="AO26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AP26" t="s">
         <v>79</v>
       </c>
       <c r="AQ26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS26" t="s">
         <v>79</v>
@@ -4540,13 +4507,13 @@
         <v>79</v>
       </c>
       <c r="AU26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:49">
@@ -4572,10 +4539,10 @@
         <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J27" t="s">
         <v>80</v>
@@ -4653,31 +4620,31 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AK27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AO27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AP27" t="s">
         <v>79</v>
       </c>
       <c r="AQ27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR27" t="s">
         <v>79</v>
@@ -4689,13 +4656,13 @@
         <v>79</v>
       </c>
       <c r="AU27" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AV27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW27" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:49">
@@ -4769,13 +4736,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y28" t="s">
         <v>80</v>
       </c>
       <c r="Z28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA28" t="s">
         <v>79</v>
@@ -4796,13 +4763,13 @@
         <v>80</v>
       </c>
       <c r="AG28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AJ28" t="s">
         <v>79</v>
@@ -4814,10 +4781,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AN28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s">
         <v>80</v>
@@ -4838,13 +4805,13 @@
         <v>79</v>
       </c>
       <c r="AU28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:49">
@@ -4924,10 +4891,10 @@
         <v>79</v>
       </c>
       <c r="Z29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AA29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB29" t="s">
         <v>79</v>
@@ -4987,13 +4954,13 @@
         <v>79</v>
       </c>
       <c r="AU29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AV29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AW29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:49">
@@ -5004,7 +4971,7 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
         <v>80</v>
@@ -5031,10 +4998,10 @@
         <v>80</v>
       </c>
       <c r="L30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N30" t="s">
         <v>79</v>
@@ -5061,10 +5028,10 @@
         <v>80</v>
       </c>
       <c r="V30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="W30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X30" t="s">
         <v>79</v>
@@ -5076,13 +5043,13 @@
         <v>79</v>
       </c>
       <c r="AA30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AB30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AC30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AD30" t="s">
         <v>79</v>
@@ -5094,13 +5061,13 @@
         <v>79</v>
       </c>
       <c r="AG30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s">
         <v>79</v>
@@ -5127,7 +5094,7 @@
         <v>80</v>
       </c>
       <c r="AR30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AS30" t="s">
         <v>79</v>
@@ -5136,13 +5103,13 @@
         <v>79</v>
       </c>
       <c r="AU30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AV30" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AW30" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:49">
@@ -5228,7 +5195,7 @@
         <v>80</v>
       </c>
       <c r="AB31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s">
         <v>80</v>
@@ -5249,10 +5216,10 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="s">
         <v>80</v>
@@ -5261,16 +5228,16 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AO31" t="s">
         <v>80</v>
       </c>
       <c r="AP31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AQ31" t="s">
         <v>80</v>
@@ -5279,19 +5246,19 @@
         <v>80</v>
       </c>
       <c r="AS31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AT31" t="s">
         <v>80</v>
       </c>
       <c r="AU31" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AV31" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AW31" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_(local)_percentile_classification_matrix.xlsx
+++ b/outputs/Sorghum_(local)_percentile_classification_matrix.xlsx
@@ -256,7 +256,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
